--- a/salidas/empresas/BMY.xlsx
+++ b/salidas/empresas/BMY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>10.63312339782715</v>
+        <v>10.63312149047852</v>
       </c>
       <c r="C3" t="n">
         <v>23.10000038146973</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.3281888961792</v>
+        <v>11.32819080352783</v>
       </c>
       <c r="C4" t="n">
         <v>24.61000061035156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.81630992889404</v>
+        <v>11.81630611419678</v>
       </c>
       <c r="C5" t="n">
         <v>25.3799991607666</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.42988014221191</v>
+        <v>11.42988109588623</v>
       </c>
       <c r="C6" t="n">
         <v>24.54999923706055</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.03978824615479</v>
+        <v>12.0397891998291</v>
       </c>
       <c r="C7" t="n">
         <v>25.86000061035156</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.28257751464844</v>
+        <v>11.28257846832275</v>
       </c>
       <c r="C8" t="n">
         <v>23.96999931335449</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.72974014282227</v>
+        <v>11.72973823547363</v>
       </c>
       <c r="C10" t="n">
         <v>24.92000007629395</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>11.7826452255249</v>
+        <v>11.78264236450195</v>
       </c>
       <c r="C11" t="n">
         <v>24.75</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>11.82073593139648</v>
+        <v>11.82072925567627</v>
       </c>
       <c r="C12" t="n">
         <v>24.82999992370605</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.53007125854492</v>
+        <v>12.53006458282471</v>
       </c>
       <c r="C13" t="n">
         <v>26.31999969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.85333633422852</v>
+        <v>13.8533296585083</v>
       </c>
       <c r="C14" t="n">
         <v>28.79000091552734</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>12.69367122650146</v>
+        <v>12.69367027282715</v>
       </c>
       <c r="C15" t="n">
         <v>26.3799991607666</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.35770702362061</v>
+        <v>13.35771465301514</v>
       </c>
       <c r="C16" t="n">
         <v>27.76000022888184</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.02789306640625</v>
+        <v>14.0278959274292</v>
       </c>
       <c r="C17" t="n">
         <v>28.86000061035156</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.73269081115723</v>
+        <v>14.73268985748291</v>
       </c>
       <c r="C18" t="n">
         <v>30.30999946594238</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>13.93167591094971</v>
+        <v>13.93167781829834</v>
       </c>
       <c r="C20" t="n">
         <v>28.40999984741211</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.29456329345703</v>
+        <v>14.29456043243408</v>
       </c>
       <c r="C21" t="n">
         <v>29.14999961853027</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>14.13274192810059</v>
+        <v>14.13273620605469</v>
       </c>
       <c r="C22" t="n">
         <v>28.81999969482422</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.8493070602417</v>
+        <v>14.84930324554443</v>
       </c>
       <c r="C23" t="n">
         <v>29.98999977111816</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>14.67105293273926</v>
+        <v>14.67106246948242</v>
       </c>
       <c r="C24" t="n">
         <v>29.6299991607666</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.53297996520996</v>
+        <v>11.53298568725586</v>
       </c>
       <c r="C26" t="n">
         <v>23.02000045776367</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.32757186889648</v>
+        <v>11.32757472991943</v>
       </c>
       <c r="C27" t="n">
         <v>22.61000061035156</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.67126274108887</v>
+        <v>10.67126655578613</v>
       </c>
       <c r="C28" t="n">
         <v>21.29999923706055</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>11.1629524230957</v>
+        <v>11.16295337677002</v>
       </c>
       <c r="C29" t="n">
         <v>21.96999931335449</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.57959938049316</v>
+        <v>11.57959365844727</v>
       </c>
       <c r="C30" t="n">
         <v>22.79000091552734</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.43128967285156</v>
+        <v>10.4312915802002</v>
       </c>
       <c r="C31" t="n">
         <v>20.53000068664551</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>10.89318656921387</v>
+        <v>10.89318561553955</v>
       </c>
       <c r="C32" t="n">
         <v>21.1200008392334</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.00665760040283</v>
+        <v>11.0066556930542</v>
       </c>
       <c r="C33" t="n">
         <v>21.34000015258789</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.75392723083496</v>
+        <v>10.75392436981201</v>
       </c>
       <c r="C34" t="n">
         <v>20.85000038146973</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>10.75915908813477</v>
+        <v>10.75916385650635</v>
       </c>
       <c r="C35" t="n">
         <v>20.54999923706055</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.36297130584717</v>
+        <v>11.36297702789307</v>
       </c>
       <c r="C38" t="n">
         <v>21.40999984741211</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.770781517028809</v>
+        <v>9.770777702331543</v>
       </c>
       <c r="C39" t="n">
         <v>18.40999984741211</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>11.63364887237549</v>
+        <v>11.6336498260498</v>
       </c>
       <c r="C40" t="n">
         <v>21.92000007629395</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.33623695373535</v>
+        <v>10.33623600006104</v>
       </c>
       <c r="C41" t="n">
         <v>19.20000076293945</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.72384262084961</v>
+        <v>10.72384548187256</v>
       </c>
       <c r="C42" t="n">
         <v>19.92000007629395</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.93379974365234</v>
+        <v>10.93379878997803</v>
       </c>
       <c r="C43" t="n">
         <v>20.30999946594238</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.88503837585449</v>
+        <v>11.88503742218018</v>
       </c>
       <c r="C44" t="n">
         <v>21.73999977111816</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.09825134277344</v>
+        <v>12.0982494354248</v>
       </c>
       <c r="C45" t="n">
         <v>22.1299991607666</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.48055648803711</v>
+        <v>12.48056316375732</v>
       </c>
       <c r="C46" t="n">
         <v>22.52000045776367</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.08153438568115</v>
+        <v>12.08153533935547</v>
       </c>
       <c r="C47" t="n">
         <v>21.79999923706055</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.02677440643311</v>
+        <v>14.02676963806152</v>
       </c>
       <c r="C48" t="n">
         <v>25.30999946594238</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.16892147064209</v>
+        <v>14.16891860961914</v>
       </c>
       <c r="C49" t="n">
         <v>25.25</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>13.66949558258057</v>
+        <v>13.66950130462646</v>
       </c>
       <c r="C50" t="n">
         <v>24.36000061035156</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.75366973876953</v>
+        <v>13.75367450714111</v>
       </c>
       <c r="C51" t="n">
         <v>24.51000022888184</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>15.16228294372559</v>
+        <v>15.1622838973999</v>
       </c>
       <c r="C52" t="n">
         <v>26.70000076293945</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>14.3729362487793</v>
+        <v>14.37293434143066</v>
       </c>
       <c r="C53" t="n">
         <v>25.30999946594238</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>13.18039608001709</v>
+        <v>13.18039226531982</v>
       </c>
       <c r="C54" t="n">
         <v>23.20999908447266</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.34432125091553</v>
+        <v>14.34432983398438</v>
       </c>
       <c r="C55" t="n">
         <v>24.94000053405762</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.33281707763672</v>
+        <v>14.33281803131104</v>
       </c>
       <c r="C56" t="n">
         <v>24.92000007629395</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.99999523162842</v>
+        <v>14.99999809265137</v>
       </c>
       <c r="C57" t="n">
         <v>26.07999992370605</v>
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.6509370803833</v>
+        <v>15.65093994140625</v>
       </c>
       <c r="C59" t="n">
         <v>26.89999961853027</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.68511390686035</v>
+        <v>14.68511581420898</v>
       </c>
       <c r="C60" t="n">
         <v>25.23999977111816</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.40657520294189</v>
+        <v>15.40657329559326</v>
       </c>
       <c r="C61" t="n">
         <v>26.47999954223633</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>14.83494853973389</v>
+        <v>14.83495330810547</v>
       </c>
       <c r="C62" t="n">
         <v>25.18000030517578</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.20611000061035</v>
+        <v>15.20611953735352</v>
       </c>
       <c r="C63" t="n">
         <v>25.80999946594238</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.76522350311279</v>
+        <v>15.76522636413574</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>17.15504264831543</v>
+        <v>17.15505027770996</v>
       </c>
       <c r="C66" t="n">
         <v>28.76000022888184</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.47599601745605</v>
+        <v>17.47599220275879</v>
       </c>
       <c r="C67" t="n">
         <v>28.95999908447266</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>17.29495620727539</v>
+        <v>17.29495048522949</v>
       </c>
       <c r="C68" t="n">
         <v>28.65999984741211</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.95271492004395</v>
+        <v>17.95272254943848</v>
       </c>
       <c r="C69" t="n">
         <v>29.75</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.93633651733398</v>
+        <v>18.93634605407715</v>
       </c>
       <c r="C70" t="n">
         <v>31.3799991607666</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.25722503662109</v>
+        <v>19.25723266601562</v>
       </c>
       <c r="C71" t="n">
         <v>31.59000015258789</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.94608116149902</v>
+        <v>19.94608306884766</v>
       </c>
       <c r="C72" t="n">
         <v>32.72000122070312</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>21.48226547241211</v>
+        <v>21.48227310180664</v>
       </c>
       <c r="C73" t="n">
         <v>35.2400016784668</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>19.80312156677246</v>
+        <v>19.80311965942383</v>
       </c>
       <c r="C75" t="n">
         <v>32.16999816894531</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>20.77573204040527</v>
+        <v>20.77572822570801</v>
       </c>
       <c r="C76" t="n">
         <v>33.75</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>20.74998664855957</v>
+        <v>20.74998092651367</v>
       </c>
       <c r="C77" t="n">
         <v>33.36999893188477</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>20.73133277893066</v>
+        <v>20.73132705688477</v>
       </c>
       <c r="C78" t="n">
         <v>33.34000015258789</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.35427093505859</v>
+        <v>22.35427665710449</v>
       </c>
       <c r="C79" t="n">
         <v>35.95000076293945</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>22.34739685058594</v>
+        <v>22.34739875793457</v>
       </c>
       <c r="C80" t="n">
         <v>35.59999847412109</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>20.72156715393066</v>
+        <v>20.7215576171875</v>
       </c>
       <c r="C81" t="n">
         <v>33.0099983215332</v>
@@ -2306,7 +2318,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>21.0833568572998</v>
+        <v>21.08335876464844</v>
       </c>
       <c r="C83" t="n">
         <v>33.25</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.69023132324219</v>
+        <v>20.69022560119629</v>
       </c>
       <c r="C84" t="n">
         <v>32.63000106811523</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.66486358642578</v>
+        <v>20.66486167907715</v>
       </c>
       <c r="C85" t="n">
         <v>32.59000015258789</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>23.16465377807617</v>
+        <v>23.16465759277344</v>
       </c>
       <c r="C86" t="n">
         <v>36.13999938964844</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>23.69665908813477</v>
+        <v>23.6966552734375</v>
       </c>
       <c r="C87" t="n">
         <v>36.97000122070312</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.40154457092285</v>
+        <v>26.40154838562012</v>
       </c>
       <c r="C88" t="n">
         <v>41.18999862670898</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>25.67492866516113</v>
+        <v>25.67491912841797</v>
       </c>
       <c r="C89" t="n">
         <v>39.72000122070312</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.74075508117676</v>
+        <v>29.74076271057129</v>
       </c>
       <c r="C90" t="n">
         <v>46.0099983215332</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>28.88752174377441</v>
+        <v>28.88751792907715</v>
       </c>
       <c r="C91" t="n">
         <v>44.68999862670898</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>28.17022132873535</v>
+        <v>28.17023277282715</v>
       </c>
       <c r="C92" t="n">
         <v>43.2400016784668</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>27.1604175567627</v>
+        <v>27.16042327880859</v>
       </c>
       <c r="C93" t="n">
         <v>41.68999862670898</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>30.1507396697998</v>
+        <v>30.15074920654297</v>
       </c>
       <c r="C94" t="n">
         <v>46.27999877929688</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>34.47141647338867</v>
+        <v>34.47140121459961</v>
       </c>
       <c r="C95" t="n">
         <v>52.52000045776367</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>33.72317504882812</v>
+        <v>33.72316741943359</v>
       </c>
       <c r="C96" t="n">
         <v>51.38000106811523</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>35.12159729003906</v>
+        <v>35.12158966064453</v>
       </c>
       <c r="C97" t="n">
         <v>53.15000152587891</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>33.02024841308594</v>
+        <v>33.02023696899414</v>
       </c>
       <c r="C98" t="n">
         <v>49.97000122070312</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>35.53128814697266</v>
+        <v>35.53127670288086</v>
       </c>
       <c r="C99" t="n">
         <v>53.77000045776367</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.32863235473633</v>
+        <v>34.32862091064453</v>
       </c>
       <c r="C100" t="n">
         <v>51.95000076293945</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.33087539672852</v>
+        <v>33.33086776733398</v>
       </c>
       <c r="C101" t="n">
         <v>50.09000015258789</v>
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.27950286865234</v>
+        <v>32.27950668334961</v>
       </c>
       <c r="C103" t="n">
         <v>48.5099983215332</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.93539047241211</v>
+        <v>33.93538284301758</v>
       </c>
       <c r="C104" t="n">
         <v>50.61999893188477</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.95549011230469</v>
+        <v>33.95549392700195</v>
       </c>
       <c r="C105" t="n">
         <v>50.65000152587891</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>34.310791015625</v>
+        <v>34.31080627441406</v>
       </c>
       <c r="C106" t="n">
         <v>51.18000030517578</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.2866096496582</v>
+        <v>39.28661346435547</v>
       </c>
       <c r="C107" t="n">
         <v>58.18999862670898</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.86725234985352</v>
+        <v>39.86723709106445</v>
       </c>
       <c r="C108" t="n">
         <v>59.04999923706055</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.101806640625</v>
+        <v>40.10181045532227</v>
       </c>
       <c r="C109" t="n">
         <v>59.02999877929688</v>
@@ -3118,7 +3130,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>41.38577651977539</v>
+        <v>41.38578033447266</v>
       </c>
       <c r="C111" t="n">
         <v>60.91999816894531</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.81784057617188</v>
+        <v>43.81784820556641</v>
       </c>
       <c r="C112" t="n">
         <v>64.5</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>43.54452896118164</v>
+        <v>43.54452514648438</v>
       </c>
       <c r="C113" t="n">
         <v>63.72999954223633</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>44.13896942138672</v>
+        <v>44.13897323608398</v>
       </c>
       <c r="C114" t="n">
         <v>64.59999847412109</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>45.46451950073242</v>
+        <v>45.46451568603516</v>
       </c>
       <c r="C115" t="n">
         <v>66.54000091552734</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>45.10034561157227</v>
+        <v>45.10035705566406</v>
       </c>
       <c r="C116" t="n">
         <v>65.63999938964844</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>40.86102676391602</v>
+        <v>40.86102294921875</v>
       </c>
       <c r="C117" t="n">
         <v>59.47000122070312</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>40.93243026733398</v>
+        <v>40.93243789672852</v>
       </c>
       <c r="C118" t="n">
         <v>59.20000076293945</v>
@@ -3379,7 +3391,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>46.33247375488281</v>
+        <v>46.33247756958008</v>
       </c>
       <c r="C120" t="n">
         <v>67.01000213623047</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.82380294799805</v>
+        <v>47.82378768920898</v>
       </c>
       <c r="C121" t="n">
         <v>68.79000091552734</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.21450805664062</v>
+        <v>43.21452713012695</v>
       </c>
       <c r="C122" t="n">
         <v>62.15999984741211</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>43.05461120605469</v>
+        <v>43.05460739135742</v>
       </c>
       <c r="C123" t="n">
         <v>61.93000030517578</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.67475128173828</v>
+        <v>44.67474365234375</v>
       </c>
       <c r="C124" t="n">
         <v>63.88000106811523</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>50.47940063476562</v>
+        <v>50.47938537597656</v>
       </c>
       <c r="C125" t="n">
         <v>72.18000030517578</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.14369583129883</v>
+        <v>50.14369964599609</v>
       </c>
       <c r="C126" t="n">
         <v>71.69999694824219</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.71040344238281</v>
+        <v>51.71038055419922</v>
       </c>
       <c r="C127" t="n">
         <v>73.55000305175781</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>52.59626770019531</v>
+        <v>52.59625244140625</v>
       </c>
       <c r="C128" t="n">
         <v>74.80999755859375</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>40.34887313842773</v>
+        <v>40.34886932373047</v>
       </c>
       <c r="C129" t="n">
         <v>57.38999938964844</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>37.90922927856445</v>
+        <v>37.90922546386719</v>
       </c>
       <c r="C130" t="n">
         <v>53.91999816894531</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>36.04108047485352</v>
+        <v>36.04107666015625</v>
       </c>
       <c r="C131" t="n">
         <v>50.90999984741211</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>39.95596313476562</v>
+        <v>39.95595932006836</v>
       </c>
       <c r="C132" t="n">
         <v>56.43999862670898</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>41.37184524536133</v>
+        <v>41.37183380126953</v>
       </c>
       <c r="C133" t="n">
         <v>58.43999862670898</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.03199768066406</v>
+        <v>35.03200149536133</v>
       </c>
       <c r="C134" t="n">
         <v>49.15999984741211</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>40.41221237182617</v>
+        <v>40.41222763061523</v>
       </c>
       <c r="C135" t="n">
         <v>56.70999908447266</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>38.7518310546875</v>
+        <v>38.75183868408203</v>
       </c>
       <c r="C136" t="n">
         <v>54.38000106811523</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>40.2317008972168</v>
+        <v>40.23169708251953</v>
       </c>
       <c r="C137" t="n">
         <v>56.04999923706055</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>38.72436141967773</v>
+        <v>38.72435760498047</v>
       </c>
       <c r="C138" t="n">
         <v>53.95000076293945</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>39.99483108520508</v>
+        <v>39.99483489990234</v>
       </c>
       <c r="C139" t="n">
         <v>55.72000122070312</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.12687301635742</v>
+        <v>41.12686538696289</v>
       </c>
       <c r="C140" t="n">
         <v>56.90000152587891</v>
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>46.07075881958008</v>
+        <v>46.07077026367188</v>
       </c>
       <c r="C142" t="n">
         <v>63.7400016784668</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.83746337890625</v>
+        <v>44.83747100830078</v>
       </c>
       <c r="C143" t="n">
         <v>61.65999984741211</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>45.95003128051758</v>
+        <v>45.95002746582031</v>
       </c>
       <c r="C144" t="n">
         <v>63.18999862670898</v>
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,7 +4203,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>46.29545211791992</v>
+        <v>46.29545974731445</v>
       </c>
       <c r="C148" t="n">
         <v>63.25</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>38.4001350402832</v>
+        <v>38.40013122558594</v>
       </c>
       <c r="C149" t="n">
         <v>52.13000106811523</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>38.76107025146484</v>
+        <v>38.76108169555664</v>
       </c>
       <c r="C150" t="n">
         <v>52.61999893188477</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>40.76469421386719</v>
+        <v>40.76469039916992</v>
       </c>
       <c r="C151" t="n">
         <v>55.34000015258789</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.58988952636719</v>
+        <v>43.58989334106445</v>
       </c>
       <c r="C152" t="n">
         <v>58.75</v>
@@ -4365,7 +4377,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>46.06060791015625</v>
+        <v>46.06060028076172</v>
       </c>
       <c r="C154" t="n">
         <v>62.08000183105469</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>37.73938369750977</v>
+        <v>37.73938751220703</v>
       </c>
       <c r="C155" t="n">
         <v>50.54000091552734</v>
@@ -4452,7 +4464,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>38.81466293334961</v>
+        <v>38.81467056274414</v>
       </c>
       <c r="C157" t="n">
         <v>51.97999954223633</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>37.15628433227539</v>
+        <v>37.15627670288086</v>
       </c>
       <c r="C158" t="n">
         <v>49.36999893188477</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.87974548339844</v>
+        <v>38.87975692749023</v>
       </c>
       <c r="C159" t="n">
         <v>51.65999984741211</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.90695190429688</v>
+        <v>35.90695953369141</v>
       </c>
       <c r="C160" t="n">
         <v>47.70999908447266</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>35.25190734863281</v>
+        <v>35.25191879272461</v>
       </c>
       <c r="C161" t="n">
         <v>46.43000030517578</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>34.44711303710938</v>
+        <v>34.44710922241211</v>
       </c>
       <c r="C162" t="n">
         <v>45.36999893188477</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>34.43193435668945</v>
+        <v>34.43192672729492</v>
       </c>
       <c r="C163" t="n">
         <v>45.34999847412109</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>34.01701736450195</v>
+        <v>34.01700973510742</v>
       </c>
       <c r="C164" t="n">
         <v>44.40999984741211</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>36.82049179077148</v>
+        <v>36.82048034667969</v>
       </c>
       <c r="C165" t="n">
         <v>48.06999969482422</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>38.8426628112793</v>
+        <v>38.84266662597656</v>
       </c>
       <c r="C166" t="n">
         <v>50.70999908447266</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>44.31327056884766</v>
+        <v>44.31326675415039</v>
       </c>
       <c r="C167" t="n">
         <v>57.36999893188477</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>43.98113632202148</v>
+        <v>43.98114395141602</v>
       </c>
       <c r="C168" t="n">
         <v>56.93999862670898</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>49.58111572265625</v>
+        <v>49.58112335205078</v>
       </c>
       <c r="C169" t="n">
         <v>64.19000244140625</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>48.96661376953125</v>
+        <v>48.96660614013672</v>
       </c>
       <c r="C170" t="n">
         <v>62.95000076293945</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>45.94070816040039</v>
+        <v>45.94071197509766</v>
       </c>
       <c r="C171" t="n">
         <v>59.06000137329102</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>43.35820770263672</v>
+        <v>43.35820007324219</v>
       </c>
       <c r="C172" t="n">
         <v>55.7400016784668</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>47.6934700012207</v>
+        <v>47.69347763061523</v>
       </c>
       <c r="C173" t="n">
         <v>60.81000137329102</v>
@@ -4974,7 +4986,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,7 +5044,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>49.15585327148438</v>
+        <v>49.15586090087891</v>
       </c>
       <c r="C177" t="n">
         <v>62.20000076293945</v>
@@ -5088,11 +5100,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.64641952514648</v>
+        <v>47.64640808105469</v>
       </c>
       <c r="C178" t="n">
         <v>60.29000091552734</v>
@@ -5115,11 +5127,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.53965759277344</v>
+        <v>46.5396614074707</v>
       </c>
       <c r="C179" t="n">
         <v>58.45000076293945</v>
@@ -5142,7 +5154,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5169,11 +5181,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>49.78411483764648</v>
+        <v>49.78413009643555</v>
       </c>
       <c r="C181" t="n">
         <v>62.02999877929688</v>
@@ -5196,11 +5208,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>49.30257415771484</v>
+        <v>49.30258178710938</v>
       </c>
       <c r="C182" t="n">
         <v>61.43000030517578</v>
@@ -5223,11 +5235,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>49.22231292724609</v>
+        <v>49.22230911254883</v>
       </c>
       <c r="C183" t="n">
         <v>61.33000183105469</v>
@@ -5250,11 +5262,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>51.06217193603516</v>
+        <v>51.06216430664062</v>
       </c>
       <c r="C184" t="n">
         <v>63.13000106811523</v>
@@ -5277,11 +5289,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>50.48788452148438</v>
+        <v>50.48789215087891</v>
       </c>
       <c r="C185" t="n">
         <v>62.41999816894531</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>53.15706634521484</v>
+        <v>53.15706253051758</v>
       </c>
       <c r="C186" t="n">
         <v>65.72000122070312</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>54.04679107666016</v>
+        <v>54.04678726196289</v>
       </c>
       <c r="C187" t="n">
         <v>66.81999969482422</v>
@@ -5358,11 +5370,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>55.30162048339844</v>
+        <v>55.30160903930664</v>
       </c>
       <c r="C188" t="n">
         <v>67.87000274658203</v>
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>54.4786376953125</v>
+        <v>54.47864532470703</v>
       </c>
       <c r="C189" t="n">
         <v>66.86000061035156</v>
@@ -5412,11 +5424,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>48.60559463500977</v>
+        <v>48.6055908203125</v>
       </c>
       <c r="C190" t="n">
         <v>59.16999816894531</v>
@@ -5439,11 +5451,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>47.97307968139648</v>
+        <v>47.97306823730469</v>
       </c>
       <c r="C191" t="n">
         <v>58.40000152587891</v>
@@ -5466,11 +5478,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.05472564697266</v>
+        <v>44.05471801757812</v>
       </c>
       <c r="C192" t="n">
         <v>53.63000106811523</v>
@@ -5493,11 +5505,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>51.21782684326172</v>
+        <v>51.21782302856445</v>
       </c>
       <c r="C193" t="n">
         <v>62.34999847412109</v>
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.77144622802734</v>
+        <v>53.77145004272461</v>
       </c>
       <c r="C194" t="n">
         <v>64.88999938964844</v>
@@ -5547,7 +5559,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5576,11 +5588,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>60.96327209472656</v>
+        <v>60.9632682800293</v>
       </c>
       <c r="C196" t="n">
         <v>73.02999877929688</v>
@@ -5605,11 +5617,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>62.83313751220703</v>
+        <v>62.83315277099609</v>
       </c>
       <c r="C197" t="n">
         <v>75.26999664306641</v>
@@ -5634,11 +5646,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>62.9833984375</v>
+        <v>62.98340225219727</v>
       </c>
       <c r="C198" t="n">
         <v>75.44999694824219</v>
@@ -5663,11 +5675,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>64.72379302978516</v>
+        <v>64.72377777099609</v>
       </c>
       <c r="C199" t="n">
         <v>77</v>
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5721,7 +5733,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5750,11 +5762,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>59.75602722167969</v>
+        <v>59.75601577758789</v>
       </c>
       <c r="C202" t="n">
         <v>71.08999633789062</v>
@@ -5779,11 +5791,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>65.61474609375</v>
+        <v>65.61476898193359</v>
       </c>
       <c r="C203" t="n">
         <v>77.47000122070312</v>
@@ -5808,11 +5820,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>67.99474334716797</v>
+        <v>67.99473571777344</v>
       </c>
       <c r="C204" t="n">
         <v>80.27999877929688</v>
@@ -5837,11 +5849,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>60.9394645690918</v>
+        <v>60.93948364257812</v>
       </c>
       <c r="C205" t="n">
         <v>71.94999694824219</v>
@@ -5866,11 +5878,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>62.0191535949707</v>
+        <v>62.01916122436523</v>
       </c>
       <c r="C206" t="n">
         <v>72.65000152587891</v>
@@ -5895,11 +5907,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>58.86910247802734</v>
+        <v>58.86911010742188</v>
       </c>
       <c r="C207" t="n">
         <v>68.95999908447266</v>
@@ -5924,11 +5936,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>59.16789245605469</v>
+        <v>59.16789627075195</v>
       </c>
       <c r="C208" t="n">
         <v>69.30999755859375</v>
@@ -5953,11 +5965,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>57.46874237060547</v>
+        <v>57.46873092651367</v>
       </c>
       <c r="C209" t="n">
         <v>66.76999664306641</v>
@@ -5982,7 +5994,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6011,11 +6023,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>55.04157257080078</v>
+        <v>55.04156494140625</v>
       </c>
       <c r="C211" t="n">
         <v>63.95000076293945</v>
@@ -6040,11 +6052,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>54.00227737426758</v>
+        <v>54.00227355957031</v>
       </c>
       <c r="C212" t="n">
         <v>62.18999862670898</v>
@@ -6069,11 +6081,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>53.53337478637695</v>
+        <v>53.53337097167969</v>
       </c>
       <c r="C213" t="n">
         <v>61.65000152587891</v>
@@ -6098,7 +6110,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6127,11 +6139,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.19989395141602</v>
+        <v>45.19988632202148</v>
       </c>
       <c r="C215" t="n">
         <v>51.52999877929688</v>
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6185,11 +6197,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>45.00691986083984</v>
+        <v>45.00691604614258</v>
       </c>
       <c r="C217" t="n">
         <v>51.31000137329102</v>
@@ -6214,7 +6226,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6243,11 +6255,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>45.03232955932617</v>
+        <v>45.03233337402344</v>
       </c>
       <c r="C219" t="n">
         <v>50.75</v>
@@ -6272,11 +6284,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>48.12025833129883</v>
+        <v>48.12026214599609</v>
       </c>
       <c r="C220" t="n">
         <v>54.22999954223633</v>
@@ -6301,11 +6313,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>39.44310760498047</v>
+        <v>39.4431037902832</v>
       </c>
       <c r="C221" t="n">
         <v>43.93999862670898</v>
@@ -6328,11 +6340,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>36.88478851318359</v>
+        <v>36.88478088378906</v>
       </c>
       <c r="C222" t="n">
         <v>41.09000015258789</v>
@@ -6355,11 +6367,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>37.27975082397461</v>
+        <v>37.27975463867188</v>
       </c>
       <c r="C223" t="n">
         <v>41.52999877929688</v>
@@ -6382,7 +6394,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6409,11 +6421,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>45.51980972290039</v>
+        <v>45.51981353759766</v>
       </c>
       <c r="C225" t="n">
         <v>49.95000076293945</v>
@@ -6436,7 +6448,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6463,11 +6475,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>51.39254379272461</v>
+        <v>51.39254760742188</v>
       </c>
       <c r="C227" t="n">
         <v>55.77000045776367</v>
@@ -6490,11 +6502,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>54.57174301147461</v>
+        <v>54.57175064086914</v>
       </c>
       <c r="C228" t="n">
         <v>59.22000122070312</v>
@@ -6517,7 +6529,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6544,11 +6556,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>54.92255783081055</v>
+        <v>54.92255401611328</v>
       </c>
       <c r="C230" t="n">
         <v>58.95000076293945</v>
@@ -6571,11 +6583,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>55.54677963256836</v>
+        <v>55.54677581787109</v>
       </c>
       <c r="C231" t="n">
         <v>59.61999893188477</v>
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>56.82318496704102</v>
+        <v>56.82318115234375</v>
       </c>
       <c r="C232" t="n">
         <v>60.9900016784668</v>
@@ -6625,11 +6637,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>47.27730178833008</v>
+        <v>47.27730560302734</v>
       </c>
       <c r="C233" t="n">
         <v>50.20000076293945</v>
@@ -6654,11 +6666,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>45.46908950805664</v>
+        <v>45.46908569335938</v>
       </c>
       <c r="C234" t="n">
         <v>48.27999877929688</v>
@@ -6683,11 +6695,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>43.59494781494141</v>
+        <v>43.59495162963867</v>
       </c>
       <c r="C235" t="n">
         <v>46.29000091552734</v>
@@ -6712,7 +6724,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6741,7 +6753,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6770,11 +6782,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>43.0344123840332</v>
+        <v>43.03440856933594</v>
       </c>
       <c r="C238" t="n">
         <v>45.09999847412109</v>
@@ -6799,7 +6811,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6828,7 +6840,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6857,7 +6869,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6886,7 +6898,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6915,7 +6927,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6944,7 +6956,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6973,7 +6985,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7002,7 +7014,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7031,7 +7043,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7060,7 +7072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7089,7 +7101,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7118,32 +7130,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>61.15000152587891</v>
+        <v>61.5</v>
       </c>
       <c r="C250" t="n">
-        <v>61.15000152587891</v>
+        <v>61.5</v>
       </c>
       <c r="D250" t="n">
-        <v>168776200</v>
+        <v>183678100</v>
       </c>
       <c r="E250" t="n">
         <v>4.55</v>
       </c>
       <c r="F250" t="n">
-        <v>13.43956077491844</v>
+        <v>13.51648351648352</v>
       </c>
       <c r="G250" t="n">
         <v>2042714656</v>
       </c>
       <c r="H250" t="n">
-        <v>124912004331.3352</v>
+        <v>125626951344</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08262348316944763</v>
+        <v>0.08991862836078854</v>
       </c>
     </row>
   </sheetData>
@@ -7175,75 +7187,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7279,13 +7291,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7480,7 +7492,7 @@
       <c r="I7" t="n">
         <v>5.35</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K7" t="n">
@@ -7493,13 +7505,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7526,7 +7538,7 @@
       <c r="I8" t="n">
         <v>5.459999999999998</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K8" t="n">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40381</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7572,7 +7584,7 @@
       <c r="I9" t="n">
         <v>5.499999999999999</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K9" t="n">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7618,7 +7630,7 @@
       <c r="I10" t="n">
         <v>5.569999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7631,13 +7643,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7664,7 +7676,7 @@
       <c r="I11" t="n">
         <v>1.789999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K11" t="n">
@@ -7677,13 +7689,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7710,7 +7722,7 @@
       <c r="I12" t="n">
         <v>1.929999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="K12" t="n">
@@ -7723,13 +7735,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7756,7 +7768,7 @@
       <c r="I13" t="n">
         <v>1.919999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K13" t="n">
@@ -7769,13 +7781,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7802,7 +7814,7 @@
       <c r="I14" t="n">
         <v>1.929999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K14" t="n">
@@ -7815,13 +7827,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7848,7 +7860,7 @@
       <c r="I15" t="n">
         <v>2.149999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="K15" t="n">
@@ -7861,13 +7873,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7894,7 +7906,7 @@
       <c r="I16" t="n">
         <v>2.219999999999999</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K16" t="n">
@@ -7907,13 +7919,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7940,7 +7952,7 @@
       <c r="I17" t="n">
         <v>2.079999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K17" t="n">
@@ -7953,13 +7965,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7986,7 +7998,7 @@
       <c r="I18" t="n">
         <v>1.089999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K18" t="n">
@@ -7999,13 +8011,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8032,7 +8044,7 @@
       <c r="I19" t="n">
         <v>1.149999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K19" t="n">
@@ -8045,13 +8057,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8078,7 +8090,7 @@
       <c r="I20" t="n">
         <v>0.8799999999999991</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K20" t="n">
@@ -8091,13 +8103,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8124,7 +8136,7 @@
       <c r="I21" t="n">
         <v>0.8199999999999992</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K21" t="n">
@@ -8137,13 +8149,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8170,7 +8182,7 @@
       <c r="I22" t="n">
         <v>1.669999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K22" t="n">
@@ -8183,13 +8195,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8216,7 +8228,7 @@
       <c r="I23" t="n">
         <v>1.549999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K23" t="n">
@@ -8229,13 +8241,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8262,7 +8274,7 @@
       <c r="I24" t="n">
         <v>1.739999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K24" t="n">
@@ -8275,13 +8287,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8308,7 +8320,7 @@
       <c r="I25" t="n">
         <v>1.619999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K25" t="n">
@@ -8321,13 +8333,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8354,7 +8366,7 @@
       <c r="I26" t="n">
         <v>1.629999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K26" t="n">
@@ -8367,13 +8379,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8400,7 +8412,7 @@
       <c r="I27" t="n">
         <v>1.199999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K27" t="n">
@@ -8413,13 +8425,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8446,7 +8458,7 @@
       <c r="I28" t="n">
         <v>1.349999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K28" t="n">
@@ -8459,13 +8471,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8492,7 +8504,7 @@
       <c r="I29" t="n">
         <v>1.069999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K29" t="n">
@@ -8505,13 +8517,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="I30" t="n">
         <v>1.059999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K30" t="n">
@@ -8551,13 +8563,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8584,7 +8596,7 @@
       <c r="I31" t="n">
         <v>0.9299999999999988</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="K31" t="n">
@@ -8597,13 +8609,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8630,7 +8642,7 @@
       <c r="I32" t="n">
         <v>0.9299999999999988</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K32" t="n">
@@ -8643,13 +8655,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8676,7 +8688,7 @@
       <c r="I33" t="n">
         <v>1.699999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K33" t="n">
@@ -8689,13 +8701,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8722,7 +8734,7 @@
       <c r="I34" t="n">
         <v>1.999999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K34" t="n">
@@ -8735,13 +8747,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8768,7 +8780,7 @@
       <c r="I35" t="n">
         <v>2.649999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K35" t="n">
@@ -8781,13 +8793,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8814,7 +8826,7 @@
       <c r="I36" t="n">
         <v>2.879999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8827,13 +8839,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8860,7 +8872,7 @@
       <c r="I37" t="n">
         <v>2.749999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8873,13 +8885,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8906,7 +8918,7 @@
       <c r="I38" t="n">
         <v>2.539999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8919,13 +8931,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8952,7 +8964,7 @@
       <c r="I39" t="n">
         <v>0.589999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="K39" t="n">
@@ -8965,13 +8977,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="I40" t="n">
         <v>0.5599999999999991</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -9011,13 +9023,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9044,7 +9056,7 @@
       <c r="I41" t="n">
         <v>0.229999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9057,13 +9069,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9090,7 +9102,7 @@
       <c r="I42" t="n">
         <v>0.8799999999999989</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K42" t="n">
@@ -9103,13 +9115,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9136,7 +9148,7 @@
       <c r="I43" t="n">
         <v>3.009999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="K43" t="n">
@@ -9149,13 +9161,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9182,7 +9194,7 @@
       <c r="I44" t="n">
         <v>3.139999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K44" t="n">
@@ -9195,13 +9207,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9228,7 +9240,7 @@
       <c r="I45" t="n">
         <v>3.779999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K45" t="n">
@@ -9241,13 +9253,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9274,7 +9286,7 @@
       <c r="I46" t="n">
         <v>3.449999999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K46" t="n">
@@ -9287,13 +9299,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9320,7 +9332,7 @@
       <c r="I47" t="n">
         <v>2.189999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="K47" t="n">
@@ -9333,13 +9345,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9366,7 +9378,7 @@
       <c r="I48" t="n">
         <v>0.8099999999999987</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K48" t="n">
@@ -9379,13 +9391,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9412,7 +9424,7 @@
       <c r="I49" t="n">
         <v>-0.1000000000000012</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9425,13 +9437,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9458,7 +9470,7 @@
       <c r="I50" t="n">
         <v>-0.1100000000000012</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K50" t="n">
@@ -9471,13 +9483,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="I51" t="n">
         <v>-4.010000000000002</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="K51" t="n">
@@ -9517,13 +9529,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9550,7 +9562,7 @@
       <c r="I52" t="n">
         <v>-2.780000000000002</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9563,13 +9575,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9596,7 +9608,7 @@
       <c r="I53" t="n">
         <v>-2.270000000000002</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9609,13 +9621,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9642,7 +9654,7 @@
       <c r="I54" t="n">
         <v>-2.400000000000002</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K54" t="n">
@@ -9655,13 +9667,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9688,7 +9700,7 @@
       <c r="I55" t="n">
         <v>3.119999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K55" t="n">
@@ -9701,13 +9713,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9734,7 +9746,7 @@
       <c r="I56" t="n">
         <v>2.819999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9747,13 +9759,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9780,7 +9792,7 @@
       <c r="I57" t="n">
         <v>3.009999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9793,13 +9805,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="I58" t="n">
         <v>3.069999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K58" t="n">
@@ -9839,13 +9851,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9872,7 +9884,7 @@
       <c r="I59" t="n">
         <v>2.949999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K59" t="n">
@@ -9885,13 +9897,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9918,7 +9930,7 @@
       <c r="I60" t="n">
         <v>3.429999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9931,13 +9943,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9964,7 +9976,7 @@
       <c r="I61" t="n">
         <v>3.759999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9977,13 +9989,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10010,7 +10022,7 @@
       <c r="I62" t="n">
         <v>3.939999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10023,13 +10035,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10056,7 +10068,7 @@
       <c r="I63" t="n">
         <v>3.859999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="K63" t="n">
@@ -10069,13 +10081,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10102,7 +10114,7 @@
       <c r="I64" t="n">
         <v>-3.100000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10115,13 +10127,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="I65" t="n">
         <v>-3.260000000000002</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K65" t="n">
@@ -10161,13 +10173,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10194,7 +10206,7 @@
       <c r="I66" t="n">
         <v>-3.590000000000002</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10207,13 +10219,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10240,7 +10252,7 @@
       <c r="I67" t="n">
         <v>-4.410000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K67" t="n">
@@ -10253,13 +10265,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="I68" t="n">
         <v>2.679999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -10299,13 +10311,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10332,7 +10344,7 @@
       <c r="I69" t="n">
         <v>2.489999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10345,13 +10357,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10378,7 +10390,7 @@
       <c r="I70" t="n">
         <v>2.969999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10391,13 +10403,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10424,7 +10436,7 @@
       <c r="I71" t="n">
         <v>3.459999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K71" t="n">
@@ -10437,13 +10449,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10470,7 +10482,7 @@
       <c r="I72" t="n">
         <v>3.569999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10483,13 +10495,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10516,7 +10528,7 @@
       <c r="I73" t="n">
         <v>4.55</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10553,52 +10565,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="C2" t="n">
@@ -10627,10 +10639,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="C3" t="n">
@@ -10659,10 +10671,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C4" t="n">
@@ -10691,10 +10703,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="C5" t="n">
@@ -10723,10 +10735,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40381</v>
       </c>
       <c r="C6" t="n">
@@ -10755,10 +10767,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C7" t="n">
@@ -10787,10 +10799,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10819,10 +10831,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="C9" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10883,10 +10895,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C11" t="n">
@@ -10915,10 +10927,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="C12" t="n">
@@ -10947,10 +10959,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C13" t="n">
@@ -10979,10 +10991,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C14" t="n">
@@ -11011,10 +11023,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C15" t="n">
@@ -11043,10 +11055,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C16" t="n">
@@ -11075,10 +11087,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C17" t="n">
@@ -11107,10 +11119,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C18" t="n">
@@ -11139,10 +11151,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C19" t="n">
@@ -11171,10 +11183,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C20" t="n">
@@ -11203,10 +11215,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C21" t="n">
@@ -11235,10 +11247,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C22" t="n">
@@ -11267,10 +11279,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42037</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C23" t="n">
@@ -11299,10 +11311,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C24" t="n">
@@ -11331,10 +11343,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C25" t="n">
@@ -11363,10 +11375,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C26" t="n">
@@ -11395,10 +11407,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="C27" t="n">
@@ -11427,10 +11439,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C28" t="n">
@@ -11459,10 +11471,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C29" t="n">
@@ -11491,10 +11503,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C30" t="n">
@@ -11523,10 +11535,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C31" t="n">
@@ -11555,10 +11567,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C32" t="n">
@@ -11587,10 +11599,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C33" t="n">
@@ -11619,10 +11631,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C34" t="n">
@@ -11651,10 +11663,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="C35" t="n">
@@ -11683,10 +11695,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C36" t="n">
@@ -11715,10 +11727,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C37" t="n">
@@ -11747,10 +11759,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C38" t="n">
@@ -11779,10 +11791,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="C39" t="n">
@@ -11811,10 +11823,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C40" t="n">
@@ -11843,10 +11855,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C41" t="n">
@@ -11875,10 +11887,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C42" t="n">
@@ -11907,10 +11919,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43864</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="C43" t="n">
@@ -11939,10 +11951,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C44" t="n">
@@ -11971,10 +11983,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C45" t="n">
@@ -12003,10 +12015,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C46" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="C47" t="n">
@@ -12067,10 +12079,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C48" t="n">
@@ -12099,10 +12111,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C49" t="n">
@@ -12131,10 +12143,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C50" t="n">
@@ -12163,10 +12175,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C51" t="n">
@@ -12195,10 +12207,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C52" t="n">
@@ -12227,10 +12239,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C53" t="n">
@@ -12259,10 +12271,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C54" t="n">
@@ -12291,10 +12303,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44964</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C55" t="n">
@@ -12323,10 +12335,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C56" t="n">
@@ -12355,10 +12367,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45127</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12387,10 +12399,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C58" t="n">
@@ -12419,10 +12431,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45328</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="C59" t="n">
@@ -12451,10 +12463,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C60" t="n">
@@ -12483,10 +12495,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C61" t="n">
@@ -12515,10 +12527,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C62" t="n">
@@ -12547,10 +12559,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45694</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C63" t="n">
@@ -12579,10 +12591,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C64" t="n">
@@ -12611,10 +12623,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45862</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C65" t="n">
@@ -12643,10 +12655,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C66" t="n">
@@ -12675,10 +12687,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46057</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C67" t="n">
@@ -12707,10 +12719,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C68" t="n">
@@ -12739,10 +12751,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46225</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C69" t="n">
@@ -12789,12 +12801,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BMY.xlsx
+++ b/salidas/empresas/BMY.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.49042987823486</v>
+        <v>10.4904317855835</v>
       </c>
       <c r="C2" t="n">
         <v>22.79000091552734</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.32819080352783</v>
+        <v>11.3281888961792</v>
       </c>
       <c r="C4" t="n">
         <v>24.61000061035156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.81630611419678</v>
+        <v>11.81630420684814</v>
       </c>
       <c r="C5" t="n">
         <v>25.3799991607666</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.42988109588623</v>
+        <v>11.4298791885376</v>
       </c>
       <c r="C6" t="n">
         <v>24.54999923706055</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0397891998291</v>
+        <v>12.03978633880615</v>
       </c>
       <c r="C7" t="n">
         <v>25.86000061035156</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.28257846832275</v>
+        <v>11.28257465362549</v>
       </c>
       <c r="C8" t="n">
         <v>23.96999931335449</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.23763656616211</v>
+        <v>10.23763465881348</v>
       </c>
       <c r="C9" t="n">
         <v>21.75</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.72973823547363</v>
+        <v>11.729736328125</v>
       </c>
       <c r="C10" t="n">
         <v>24.92000007629395</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>11.82072925567627</v>
+        <v>11.82072639465332</v>
       </c>
       <c r="C12" t="n">
         <v>24.82999992370605</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.53006458282471</v>
+        <v>12.53006935119629</v>
       </c>
       <c r="C13" t="n">
         <v>26.31999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.8533296585083</v>
+        <v>13.85333061218262</v>
       </c>
       <c r="C14" t="n">
         <v>28.79000091552734</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>12.69367027282715</v>
+        <v>12.69367218017578</v>
       </c>
       <c r="C15" t="n">
         <v>26.3799991607666</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.35771465301514</v>
+        <v>13.35770797729492</v>
       </c>
       <c r="C16" t="n">
         <v>27.76000022888184</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.0278959274292</v>
+        <v>14.02789211273193</v>
       </c>
       <c r="C17" t="n">
         <v>28.86000061035156</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.73268985748291</v>
+        <v>14.73269176483154</v>
       </c>
       <c r="C18" t="n">
         <v>30.30999946594238</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.3402738571167</v>
+        <v>15.34027767181396</v>
       </c>
       <c r="C19" t="n">
         <v>31.55999946594238</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>13.93167781829834</v>
+        <v>13.93167495727539</v>
       </c>
       <c r="C20" t="n">
         <v>28.40999984741211</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.29456043243408</v>
+        <v>14.29456329345703</v>
       </c>
       <c r="C21" t="n">
         <v>29.14999961853027</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>14.13273620605469</v>
+        <v>14.13273239135742</v>
       </c>
       <c r="C22" t="n">
         <v>28.81999969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.84930324554443</v>
+        <v>14.84930992126465</v>
       </c>
       <c r="C23" t="n">
         <v>29.98999977111816</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>14.67106246948242</v>
+        <v>14.67106056213379</v>
       </c>
       <c r="C24" t="n">
         <v>29.6299991607666</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>13.13116931915283</v>
+        <v>13.13116550445557</v>
       </c>
       <c r="C25" t="n">
         <v>26.52000045776367</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>11.53298568725586</v>
+        <v>11.53298664093018</v>
       </c>
       <c r="C26" t="n">
         <v>23.02000045776367</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>11.32757472991943</v>
+        <v>11.3275728225708</v>
       </c>
       <c r="C27" t="n">
         <v>22.61000061035156</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.67126655578613</v>
+        <v>10.67126178741455</v>
       </c>
       <c r="C28" t="n">
         <v>21.29999923706055</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>11.16295337677002</v>
+        <v>11.16295433044434</v>
       </c>
       <c r="C29" t="n">
         <v>21.96999931335449</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>11.57959365844727</v>
+        <v>11.57958793640137</v>
       </c>
       <c r="C30" t="n">
         <v>22.79000091552734</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>10.4312915802002</v>
+        <v>10.4312858581543</v>
       </c>
       <c r="C31" t="n">
         <v>20.53000068664551</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>10.89318561553955</v>
+        <v>10.8931884765625</v>
       </c>
       <c r="C32" t="n">
         <v>21.1200008392334</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>11.0066556930542</v>
+        <v>11.00665473937988</v>
       </c>
       <c r="C33" t="n">
         <v>21.34000015258789</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.75392436981201</v>
+        <v>10.75392723083496</v>
       </c>
       <c r="C34" t="n">
         <v>20.85000038146973</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.83769512176514</v>
+        <v>10.83769416809082</v>
       </c>
       <c r="C36" t="n">
         <v>20.70000076293945</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>12.33952617645264</v>
+        <v>12.33952236175537</v>
       </c>
       <c r="C37" t="n">
         <v>23.25</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.36297702789307</v>
+        <v>11.36297988891602</v>
       </c>
       <c r="C38" t="n">
         <v>21.40999984741211</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.770777702331543</v>
+        <v>9.770783424377441</v>
       </c>
       <c r="C39" t="n">
         <v>18.40999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.33623600006104</v>
+        <v>10.33623790740967</v>
       </c>
       <c r="C41" t="n">
         <v>19.20000076293945</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>10.72384548187256</v>
+        <v>10.72383975982666</v>
       </c>
       <c r="C42" t="n">
         <v>19.92000007629395</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.93379878997803</v>
+        <v>10.93380355834961</v>
       </c>
       <c r="C43" t="n">
         <v>20.30999946594238</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.88503742218018</v>
+        <v>11.88503837585449</v>
       </c>
       <c r="C44" t="n">
         <v>21.73999977111816</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.0982494354248</v>
+        <v>12.09825038909912</v>
       </c>
       <c r="C45" t="n">
         <v>22.1299991607666</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.48056316375732</v>
+        <v>12.48055171966553</v>
       </c>
       <c r="C46" t="n">
         <v>22.52000045776367</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>12.08153533935547</v>
+        <v>12.08153629302979</v>
       </c>
       <c r="C47" t="n">
         <v>21.79999923706055</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.02676963806152</v>
+        <v>14.02677249908447</v>
       </c>
       <c r="C48" t="n">
         <v>25.30999946594238</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.16891860961914</v>
+        <v>14.16891956329346</v>
       </c>
       <c r="C49" t="n">
         <v>25.25</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>13.66950130462646</v>
+        <v>13.66949939727783</v>
       </c>
       <c r="C50" t="n">
         <v>24.36000061035156</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>13.75367450714111</v>
+        <v>13.75367641448975</v>
       </c>
       <c r="C51" t="n">
         <v>24.51000022888184</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>15.1622838973999</v>
+        <v>15.16228199005127</v>
       </c>
       <c r="C52" t="n">
         <v>26.70000076293945</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>14.37293434143066</v>
+        <v>14.3729362487793</v>
       </c>
       <c r="C53" t="n">
         <v>25.30999946594238</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>13.18039226531982</v>
+        <v>13.18039321899414</v>
       </c>
       <c r="C54" t="n">
         <v>23.20999908447266</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.34432983398438</v>
+        <v>14.34432411193848</v>
       </c>
       <c r="C55" t="n">
         <v>24.94000053405762</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.33281803131104</v>
+        <v>14.3328161239624</v>
       </c>
       <c r="C56" t="n">
         <v>24.92000007629395</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>14.99999809265137</v>
+        <v>14.99999523162842</v>
       </c>
       <c r="C57" t="n">
         <v>26.07999992370605</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>15.7731237411499</v>
+        <v>15.77311897277832</v>
       </c>
       <c r="C58" t="n">
         <v>27.11000061035156</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>15.65093994140625</v>
+        <v>15.65094089508057</v>
       </c>
       <c r="C59" t="n">
         <v>26.89999961853027</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.68511581420898</v>
+        <v>14.68511390686035</v>
       </c>
       <c r="C60" t="n">
         <v>25.23999977111816</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>15.40657329559326</v>
+        <v>15.40657997131348</v>
       </c>
       <c r="C61" t="n">
         <v>26.47999954223633</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>14.83495330810547</v>
+        <v>14.83494567871094</v>
       </c>
       <c r="C62" t="n">
         <v>25.18000030517578</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.20611953735352</v>
+        <v>15.20611476898193</v>
       </c>
       <c r="C63" t="n">
         <v>25.80999946594238</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>15.76522636413574</v>
+        <v>15.76522827148438</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>16.7613639831543</v>
+        <v>16.76136207580566</v>
       </c>
       <c r="C65" t="n">
         <v>28.10000038146973</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>17.47599220275879</v>
+        <v>17.47599029541016</v>
       </c>
       <c r="C67" t="n">
         <v>28.95999908447266</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>17.29495048522949</v>
+        <v>17.29495620727539</v>
       </c>
       <c r="C68" t="n">
         <v>28.65999984741211</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>17.95272254943848</v>
+        <v>17.95271873474121</v>
       </c>
       <c r="C69" t="n">
         <v>29.75</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.25723266601562</v>
+        <v>19.25723457336426</v>
       </c>
       <c r="C71" t="n">
         <v>31.59000015258789</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.94608306884766</v>
+        <v>19.94607353210449</v>
       </c>
       <c r="C72" t="n">
         <v>32.72000122070312</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>21.48227310180664</v>
+        <v>21.48226547241211</v>
       </c>
       <c r="C73" t="n">
         <v>35.2400016784668</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.84621238708496</v>
+        <v>19.84621047973633</v>
       </c>
       <c r="C74" t="n">
         <v>32.2400016784668</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>19.80311965942383</v>
+        <v>19.8031177520752</v>
       </c>
       <c r="C75" t="n">
         <v>32.16999816894531</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>20.77572822570801</v>
+        <v>20.77573394775391</v>
       </c>
       <c r="C76" t="n">
         <v>33.75</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>20.74998092651367</v>
+        <v>20.74998474121094</v>
       </c>
       <c r="C77" t="n">
         <v>33.36999893188477</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.35427665710449</v>
+        <v>22.35426712036133</v>
       </c>
       <c r="C79" t="n">
         <v>35.95000076293945</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>22.34739875793457</v>
+        <v>22.3473949432373</v>
       </c>
       <c r="C80" t="n">
         <v>35.59999847412109</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>20.7215576171875</v>
+        <v>20.7215690612793</v>
       </c>
       <c r="C81" t="n">
         <v>33.0099983215332</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>21.08335876464844</v>
+        <v>21.08336639404297</v>
       </c>
       <c r="C83" t="n">
         <v>33.25</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.69022560119629</v>
+        <v>20.69023132324219</v>
       </c>
       <c r="C84" t="n">
         <v>32.63000106811523</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.66486167907715</v>
+        <v>20.66486549377441</v>
       </c>
       <c r="C85" t="n">
         <v>32.59000015258789</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>23.16465759277344</v>
+        <v>23.16464805603027</v>
       </c>
       <c r="C86" t="n">
         <v>36.13999938964844</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.40154838562012</v>
+        <v>26.40154647827148</v>
       </c>
       <c r="C88" t="n">
         <v>41.18999862670898</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>25.67491912841797</v>
+        <v>25.67491722106934</v>
       </c>
       <c r="C89" t="n">
         <v>39.72000122070312</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.74076271057129</v>
+        <v>29.74075698852539</v>
       </c>
       <c r="C90" t="n">
         <v>46.0099983215332</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>28.88751792907715</v>
+        <v>28.88751983642578</v>
       </c>
       <c r="C91" t="n">
         <v>44.68999862670898</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>28.17023277282715</v>
+        <v>28.17022514343262</v>
       </c>
       <c r="C92" t="n">
         <v>43.2400016784668</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>30.15074920654297</v>
+        <v>30.1507396697998</v>
       </c>
       <c r="C94" t="n">
         <v>46.27999877929688</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>34.47140121459961</v>
+        <v>34.47140884399414</v>
       </c>
       <c r="C95" t="n">
         <v>52.52000045776367</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>33.72316741943359</v>
+        <v>33.72317123413086</v>
       </c>
       <c r="C96" t="n">
         <v>51.38000106811523</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>33.02023696899414</v>
+        <v>33.02024078369141</v>
       </c>
       <c r="C98" t="n">
         <v>49.97000122070312</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.32862091064453</v>
+        <v>34.32863616943359</v>
       </c>
       <c r="C100" t="n">
         <v>51.95000076293945</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.33086776733398</v>
+        <v>33.33087158203125</v>
       </c>
       <c r="C101" t="n">
         <v>50.09000015258789</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>33.09797286987305</v>
+        <v>33.09797668457031</v>
       </c>
       <c r="C102" t="n">
         <v>49.7400016784668</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.27950668334961</v>
+        <v>32.27949905395508</v>
       </c>
       <c r="C103" t="n">
         <v>48.5099983215332</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.93538284301758</v>
+        <v>33.93537139892578</v>
       </c>
       <c r="C104" t="n">
         <v>50.61999893188477</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>33.95549392700195</v>
+        <v>33.95550155639648</v>
       </c>
       <c r="C105" t="n">
         <v>50.65000152587891</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>34.31080627441406</v>
+        <v>34.310791015625</v>
       </c>
       <c r="C106" t="n">
         <v>51.18000030517578</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.28661346435547</v>
+        <v>39.28661727905273</v>
       </c>
       <c r="C107" t="n">
         <v>58.18999862670898</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.86723709106445</v>
+        <v>39.86724090576172</v>
       </c>
       <c r="C108" t="n">
         <v>59.04999923706055</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>40.10181045532227</v>
+        <v>40.10179901123047</v>
       </c>
       <c r="C109" t="n">
         <v>59.02999877929688</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>40.9442024230957</v>
+        <v>40.94421005249023</v>
       </c>
       <c r="C110" t="n">
         <v>60.27000045776367</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.81784820556641</v>
+        <v>43.81784057617188</v>
       </c>
       <c r="C112" t="n">
         <v>64.5</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>43.54452514648438</v>
+        <v>43.54452896118164</v>
       </c>
       <c r="C113" t="n">
         <v>63.72999954223633</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>45.46451568603516</v>
+        <v>45.46450424194336</v>
       </c>
       <c r="C115" t="n">
         <v>66.54000091552734</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>45.10035705566406</v>
+        <v>45.10034942626953</v>
       </c>
       <c r="C116" t="n">
         <v>65.63999938964844</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>40.93243789672852</v>
+        <v>40.93242645263672</v>
       </c>
       <c r="C118" t="n">
         <v>59.20000076293945</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>45.59955596923828</v>
+        <v>45.59955215454102</v>
       </c>
       <c r="C119" t="n">
         <v>65.94999694824219</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>46.33247756958008</v>
+        <v>46.33246994018555</v>
       </c>
       <c r="C120" t="n">
         <v>67.01000213623047</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>47.82378768920898</v>
+        <v>47.82377624511719</v>
       </c>
       <c r="C121" t="n">
         <v>68.79000091552734</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>43.21452713012695</v>
+        <v>43.21451187133789</v>
       </c>
       <c r="C122" t="n">
         <v>62.15999984741211</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>43.05460739135742</v>
+        <v>43.05461883544922</v>
       </c>
       <c r="C123" t="n">
         <v>61.93000030517578</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.67474365234375</v>
+        <v>44.67475891113281</v>
       </c>
       <c r="C124" t="n">
         <v>63.88000106811523</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>50.47938537597656</v>
+        <v>50.47940063476562</v>
       </c>
       <c r="C125" t="n">
         <v>72.18000030517578</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.14369964599609</v>
+        <v>50.14371490478516</v>
       </c>
       <c r="C126" t="n">
         <v>71.69999694824219</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.71038055419922</v>
+        <v>51.71039581298828</v>
       </c>
       <c r="C127" t="n">
         <v>73.55000305175781</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>52.59625244140625</v>
+        <v>52.59624099731445</v>
       </c>
       <c r="C128" t="n">
         <v>74.80999755859375</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>40.34886932373047</v>
+        <v>40.34886169433594</v>
       </c>
       <c r="C129" t="n">
         <v>57.38999938964844</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>36.04107666015625</v>
+        <v>36.04107284545898</v>
       </c>
       <c r="C131" t="n">
         <v>50.90999984741211</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>39.95595932006836</v>
+        <v>39.95595169067383</v>
       </c>
       <c r="C132" t="n">
         <v>56.43999862670898</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>41.37183380126953</v>
+        <v>41.37184143066406</v>
       </c>
       <c r="C133" t="n">
         <v>58.43999862670898</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.03200149536133</v>
+        <v>35.03199768066406</v>
       </c>
       <c r="C134" t="n">
         <v>49.15999984741211</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>40.41222763061523</v>
+        <v>40.41222381591797</v>
       </c>
       <c r="C135" t="n">
         <v>56.70999908447266</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>38.75183868408203</v>
+        <v>38.75183486938477</v>
       </c>
       <c r="C136" t="n">
         <v>54.38000106811523</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>40.23169708251953</v>
+        <v>40.23170852661133</v>
       </c>
       <c r="C137" t="n">
         <v>56.04999923706055</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>38.72435760498047</v>
+        <v>38.72436141967773</v>
       </c>
       <c r="C138" t="n">
         <v>53.95000076293945</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>39.99483489990234</v>
+        <v>39.99482345581055</v>
       </c>
       <c r="C139" t="n">
         <v>55.72000122070312</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.12686538696289</v>
+        <v>41.12687301635742</v>
       </c>
       <c r="C140" t="n">
         <v>56.90000152587891</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>43.71446228027344</v>
+        <v>43.7144660949707</v>
       </c>
       <c r="C141" t="n">
         <v>60.47999954223633</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>46.07077026367188</v>
+        <v>46.07075881958008</v>
       </c>
       <c r="C142" t="n">
         <v>63.7400016784668</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>44.83747100830078</v>
+        <v>44.83745956420898</v>
       </c>
       <c r="C143" t="n">
         <v>61.65999984741211</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>45.95002746582031</v>
+        <v>45.95003509521484</v>
       </c>
       <c r="C144" t="n">
         <v>63.18999862670898</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>44.56113052368164</v>
+        <v>44.56113433837891</v>
       </c>
       <c r="C145" t="n">
         <v>61.27999877929688</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>45.81969833374023</v>
+        <v>45.81968688964844</v>
       </c>
       <c r="C146" t="n">
         <v>62.59999847412109</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>48.45469284057617</v>
+        <v>48.4547004699707</v>
       </c>
       <c r="C147" t="n">
         <v>66.19999694824219</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>46.29545974731445</v>
+        <v>46.29546737670898</v>
       </c>
       <c r="C148" t="n">
         <v>63.25</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>38.40013122558594</v>
+        <v>38.40012741088867</v>
       </c>
       <c r="C149" t="n">
         <v>52.13000106811523</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>38.76108169555664</v>
+        <v>38.76107788085938</v>
       </c>
       <c r="C150" t="n">
         <v>52.61999893188477</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>43.58989334106445</v>
+        <v>43.58988952636719</v>
       </c>
       <c r="C152" t="n">
         <v>58.75</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>44.92541122436523</v>
+        <v>44.92540740966797</v>
       </c>
       <c r="C153" t="n">
         <v>60.54999923706055</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>37.73938751220703</v>
+        <v>37.73937225341797</v>
       </c>
       <c r="C155" t="n">
         <v>50.54000091552734</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>39.91981887817383</v>
+        <v>39.91982269287109</v>
       </c>
       <c r="C156" t="n">
         <v>53.45999908447266</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>38.81467056274414</v>
+        <v>38.81466674804688</v>
       </c>
       <c r="C157" t="n">
         <v>51.97999954223633</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.87975692749023</v>
+        <v>38.87975311279297</v>
       </c>
       <c r="C159" t="n">
         <v>51.65999984741211</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.90695953369141</v>
+        <v>35.90694427490234</v>
       </c>
       <c r="C160" t="n">
         <v>47.70999908447266</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>35.25191879272461</v>
+        <v>35.25191116333008</v>
       </c>
       <c r="C161" t="n">
         <v>46.43000030517578</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>34.44710922241211</v>
+        <v>34.44711685180664</v>
       </c>
       <c r="C162" t="n">
         <v>45.36999893188477</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>34.01700973510742</v>
+        <v>34.01700592041016</v>
       </c>
       <c r="C164" t="n">
         <v>44.40999984741211</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>38.84266662597656</v>
+        <v>38.84265899658203</v>
       </c>
       <c r="C166" t="n">
         <v>50.70999908447266</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>44.31326675415039</v>
+        <v>44.31327056884766</v>
       </c>
       <c r="C167" t="n">
         <v>57.36999893188477</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>43.98114395141602</v>
+        <v>43.98112869262695</v>
       </c>
       <c r="C168" t="n">
         <v>56.93999862670898</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>49.58112335205078</v>
+        <v>49.58111572265625</v>
       </c>
       <c r="C169" t="n">
         <v>64.19000244140625</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>45.94071197509766</v>
+        <v>45.94070434570312</v>
       </c>
       <c r="C171" t="n">
         <v>59.06000137329102</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>43.35820007324219</v>
+        <v>43.35818481445312</v>
       </c>
       <c r="C172" t="n">
         <v>55.7400016784668</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>47.69347763061523</v>
+        <v>47.69348526000977</v>
       </c>
       <c r="C173" t="n">
         <v>60.81000137329102</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>46.83858871459961</v>
+        <v>46.83858108520508</v>
       </c>
       <c r="C174" t="n">
         <v>59.72000122070312</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>46.11702346801758</v>
+        <v>46.11702728271484</v>
       </c>
       <c r="C175" t="n">
         <v>58.79999923706055</v>
@@ -5104,7 +5104,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>47.64640808105469</v>
+        <v>47.64641952514648</v>
       </c>
       <c r="C178" t="n">
         <v>60.29000091552734</v>
@@ -5131,7 +5131,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>46.5396614074707</v>
+        <v>46.53965377807617</v>
       </c>
       <c r="C179" t="n">
         <v>58.45000076293945</v>
@@ -5185,7 +5185,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>49.78413009643555</v>
+        <v>49.78411865234375</v>
       </c>
       <c r="C181" t="n">
         <v>62.02999877929688</v>
@@ -5212,7 +5212,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>49.30258178710938</v>
+        <v>49.30256652832031</v>
       </c>
       <c r="C182" t="n">
         <v>61.43000030517578</v>
@@ -5239,7 +5239,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>49.22230911254883</v>
+        <v>49.22231674194336</v>
       </c>
       <c r="C183" t="n">
         <v>61.33000183105469</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>53.15706253051758</v>
+        <v>53.15707015991211</v>
       </c>
       <c r="C186" t="n">
         <v>65.72000122070312</v>
@@ -5347,7 +5347,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>54.04678726196289</v>
+        <v>54.04678344726562</v>
       </c>
       <c r="C187" t="n">
         <v>66.81999969482422</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>54.47864532470703</v>
+        <v>54.4786491394043</v>
       </c>
       <c r="C189" t="n">
         <v>66.86000061035156</v>
@@ -5428,7 +5428,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>48.6055908203125</v>
+        <v>48.60559844970703</v>
       </c>
       <c r="C190" t="n">
         <v>59.16999816894531</v>
@@ -5482,7 +5482,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.05471801757812</v>
+        <v>44.05472183227539</v>
       </c>
       <c r="C192" t="n">
         <v>53.63000106811523</v>
@@ -5509,7 +5509,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>51.21782302856445</v>
+        <v>51.21782684326172</v>
       </c>
       <c r="C193" t="n">
         <v>62.34999847412109</v>
@@ -5536,7 +5536,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.77145004272461</v>
+        <v>53.77145385742188</v>
       </c>
       <c r="C194" t="n">
         <v>64.88999938964844</v>
@@ -5563,7 +5563,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>56.90376663208008</v>
+        <v>56.90377044677734</v>
       </c>
       <c r="C195" t="n">
         <v>68.66999816894531</v>
@@ -5592,7 +5592,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>60.9632682800293</v>
+        <v>60.96326065063477</v>
       </c>
       <c r="C196" t="n">
         <v>73.02999877929688</v>
@@ -5621,7 +5621,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>62.83315277099609</v>
+        <v>62.83313751220703</v>
       </c>
       <c r="C197" t="n">
         <v>75.26999664306641</v>
@@ -5650,7 +5650,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>62.98340225219727</v>
+        <v>62.98339080810547</v>
       </c>
       <c r="C198" t="n">
         <v>75.44999694824219</v>
@@ -5679,7 +5679,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>64.72377777099609</v>
+        <v>64.72379302978516</v>
       </c>
       <c r="C199" t="n">
         <v>77</v>
@@ -5708,7 +5708,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>62.01715469360352</v>
+        <v>62.01715087890625</v>
       </c>
       <c r="C200" t="n">
         <v>73.77999877929688</v>
@@ -5737,7 +5737,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>56.66273498535156</v>
+        <v>56.66274261474609</v>
       </c>
       <c r="C201" t="n">
         <v>67.41000366210938</v>
@@ -5766,7 +5766,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>59.75601577758789</v>
+        <v>59.75602722167969</v>
       </c>
       <c r="C202" t="n">
         <v>71.08999633789062</v>
@@ -5795,7 +5795,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>65.61476898193359</v>
+        <v>65.61476135253906</v>
       </c>
       <c r="C203" t="n">
         <v>77.47000122070312</v>
@@ -5853,7 +5853,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>60.93948364257812</v>
+        <v>60.93947219848633</v>
       </c>
       <c r="C205" t="n">
         <v>71.94999694824219</v>
@@ -5911,7 +5911,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>58.86911010742188</v>
+        <v>58.86911392211914</v>
       </c>
       <c r="C207" t="n">
         <v>68.95999908447266</v>
@@ -5969,7 +5969,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>57.46873092651367</v>
+        <v>57.4687385559082</v>
       </c>
       <c r="C209" t="n">
         <v>66.76999664306641</v>
@@ -5998,7 +5998,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>55.46332168579102</v>
+        <v>55.46331405639648</v>
       </c>
       <c r="C210" t="n">
         <v>64.44000244140625</v>
@@ -6027,7 +6027,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>55.04156494140625</v>
+        <v>55.04157638549805</v>
       </c>
       <c r="C211" t="n">
         <v>63.95000076293945</v>
@@ -6056,7 +6056,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>54.00227355957031</v>
+        <v>54.00227737426758</v>
       </c>
       <c r="C212" t="n">
         <v>62.18999862670898</v>
@@ -6085,7 +6085,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>53.53337097167969</v>
+        <v>53.53337860107422</v>
       </c>
       <c r="C213" t="n">
         <v>61.65000152587891</v>
@@ -6143,7 +6143,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.19988632202148</v>
+        <v>45.19988250732422</v>
       </c>
       <c r="C215" t="n">
         <v>51.52999877929688</v>
@@ -6172,7 +6172,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>43.31399917602539</v>
+        <v>43.31400299072266</v>
       </c>
       <c r="C216" t="n">
         <v>49.38000106811523</v>
@@ -6201,7 +6201,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>45.00691604614258</v>
+        <v>45.00691223144531</v>
       </c>
       <c r="C217" t="n">
         <v>51.31000137329102</v>
@@ -6230,7 +6230,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>43.36413955688477</v>
+        <v>43.3641357421875</v>
       </c>
       <c r="C218" t="n">
         <v>48.86999893188477</v>
@@ -6317,7 +6317,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>39.4431037902832</v>
+        <v>39.44310760498047</v>
       </c>
       <c r="C221" t="n">
         <v>43.93999862670898</v>
@@ -6344,7 +6344,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>36.88478088378906</v>
+        <v>36.88478469848633</v>
       </c>
       <c r="C222" t="n">
         <v>41.09000015258789</v>
@@ -6371,7 +6371,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>37.27975463867188</v>
+        <v>37.27975845336914</v>
       </c>
       <c r="C223" t="n">
         <v>41.52999877929688</v>
@@ -6398,7 +6398,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>43.34178924560547</v>
+        <v>43.34179306030273</v>
       </c>
       <c r="C224" t="n">
         <v>47.56000137329102</v>
@@ -6452,7 +6452,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>47.15105438232422</v>
+        <v>47.15105056762695</v>
       </c>
       <c r="C226" t="n">
         <v>51.7400016784668</v>
@@ -6587,7 +6587,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>55.54677581787109</v>
+        <v>55.54677963256836</v>
       </c>
       <c r="C231" t="n">
         <v>59.61999893188477</v>
@@ -6614,7 +6614,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>56.82318115234375</v>
+        <v>56.82318496704102</v>
       </c>
       <c r="C232" t="n">
         <v>60.9900016784668</v>
@@ -6699,7 +6699,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>43.59495162963867</v>
+        <v>43.59494781494141</v>
       </c>
       <c r="C235" t="n">
         <v>46.29000091552734</v>
@@ -6728,7 +6728,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>41.32639694213867</v>
+        <v>41.32639312744141</v>
       </c>
       <c r="C236" t="n">
         <v>43.31000137329102</v>
@@ -6757,7 +6757,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>45.01914596557617</v>
+        <v>45.01914215087891</v>
       </c>
       <c r="C237" t="n">
         <v>47.18000030517578</v>
@@ -6786,7 +6786,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>43.03440856933594</v>
+        <v>43.03440475463867</v>
       </c>
       <c r="C238" t="n">
         <v>45.09999847412109</v>
@@ -6815,7 +6815,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>44.56417465209961</v>
+        <v>44.56417846679688</v>
       </c>
       <c r="C239" t="n">
         <v>46.06999969482422</v>
@@ -6844,7 +6844,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>47.59187698364258</v>
+        <v>47.59187316894531</v>
       </c>
       <c r="C240" t="n">
         <v>49.20000076293945</v>
